--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116881915</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90744</v>
+        <v>90754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92055</v>
+        <v>92065</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90744</v>
+        <v>90754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116881915</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>116881914</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90754</v>
+        <v>90766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>116881913</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90754</v>
+        <v>90766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90766</v>
+        <v>90773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90766</v>
+        <v>90773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116881915</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -784,7 +779,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,11 +793,6 @@
       </c>
       <c r="E3" t="n">
         <v>221945</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -906,11 +896,6 @@
       <c r="E4" t="n">
         <v>103015</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Regulus regulus</t>
@@ -997,7 +982,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90773</v>
+        <v>90778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,11 +996,6 @@
       </c>
       <c r="E5" t="n">
         <v>5447</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1118,11 +1098,6 @@
       <c r="E6" t="n">
         <v>100049</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1209,7 +1184,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,11 +1198,6 @@
       </c>
       <c r="E7" t="n">
         <v>4364</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1315,7 +1285,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90773</v>
+        <v>90778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,11 +1299,6 @@
       </c>
       <c r="E8" t="n">
         <v>5447</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1523,7 +1488,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,11 +1502,6 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116881915</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -779,7 +784,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,6 +798,11 @@
       </c>
       <c r="E3" t="n">
         <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -881,7 +891,7 @@
         <v>116881914</v>
       </c>
       <c r="B4" t="n">
-        <v>57749</v>
+        <v>57753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,6 +905,11 @@
       </c>
       <c r="E4" t="n">
         <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -982,7 +997,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90778</v>
+        <v>90791</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -996,6 +1011,11 @@
       </c>
       <c r="E5" t="n">
         <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1083,7 +1103,7 @@
         <v>116881913</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1097,6 +1117,11 @@
       </c>
       <c r="E6" t="n">
         <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1184,7 +1209,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,6 +1223,11 @@
       </c>
       <c r="E7" t="n">
         <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1285,7 +1315,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90778</v>
+        <v>90791</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,6 +1329,11 @@
       </c>
       <c r="E8" t="n">
         <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1488,7 +1523,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1502,6 +1537,11 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90791</v>
+        <v>90804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92100</v>
+        <v>92113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90791</v>
+        <v>90804</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90804</v>
+        <v>90798</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90804</v>
+        <v>90798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116881915</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97194</v>
+        <v>97195</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>116881914</v>
       </c>
       <c r="B4" t="n">
-        <v>57753</v>
+        <v>57754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90798</v>
+        <v>90799</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>116881913</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90798</v>
+        <v>90799</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 14328-2024 artfynd.xlsx
+++ b/artfynd/A 14328-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116881915</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>116881912</v>
       </c>
       <c r="B3" t="n">
-        <v>97195</v>
+        <v>97198</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>116881910</v>
       </c>
       <c r="B5" t="n">
-        <v>90799</v>
+        <v>90802</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>117178389</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92118</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>117178391</v>
       </c>
       <c r="B8" t="n">
-        <v>90799</v>
+        <v>90802</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>117229741</v>
       </c>
       <c r="B10" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
